--- a/transportation_request_forms/016_winter_break_transportation_survey--transportation_request_forms.xlsx
+++ b/transportation_request_forms/016_winter_break_transportation_survey--transportation_request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -895,8 +895,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -924,12 +924,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'university_of_winter'}</t>
+          <t>university_of_winter</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'University of Winter'}</t>
+          <t>University of Winter</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'winter_campus'}</t>
+          <t>winter_campus</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Winter Campus'}</t>
+          <t>Winter Campus</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'other_campus'}</t>
+          <t>other_campus</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Other Campus'}</t>
+          <t>Other Campus</t>
         </is>
       </c>
     </row>
@@ -975,12 +975,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'private_vehicle'}</t>
+          <t>private_vehicle</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Private Vehicle'}</t>
+          <t>Private Vehicle</t>
         </is>
       </c>
     </row>
@@ -992,12 +992,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'public_transportation'}</t>
+          <t>public_transportation</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Public Transportation'}</t>
+          <t>Public Transportation</t>
         </is>
       </c>
     </row>
@@ -1009,12 +1009,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'carpool'}</t>
+          <t>carpool</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Carpool'}</t>
+          <t>Carpool</t>
         </is>
       </c>
     </row>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'other_arrangement'}</t>
+          <t>other_arrangement</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Other Arrangement'}</t>
+          <t>Other Arrangement</t>
         </is>
       </c>
     </row>
@@ -1043,12 +1043,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'drive'}</t>
+          <t>drive</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Drive'}</t>
+          <t>Drive</t>
         </is>
       </c>
     </row>
@@ -1060,12 +1060,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'fly'}</t>
+          <t>fly</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Fly'}</t>
+          <t>Fly</t>
         </is>
       </c>
     </row>
@@ -1077,12 +1077,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'train'}</t>
+          <t>train</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Train'}</t>
+          <t>Train</t>
         </is>
       </c>
     </row>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'bus'}</t>
+          <t>bus</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Bus'}</t>
+          <t>Bus</t>
         </is>
       </c>
     </row>
@@ -1111,12 +1111,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'staff'}</t>
+          <t>staff</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Staff'}</t>
+          <t>Staff</t>
         </is>
       </c>
     </row>
@@ -1128,12 +1128,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'faculty'}</t>
+          <t>faculty</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Faculty'}</t>
+          <t>Faculty</t>
         </is>
       </c>
     </row>
@@ -1145,12 +1145,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'students'}</t>
+          <t>students</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Students'}</t>
+          <t>Students</t>
         </is>
       </c>
     </row>
@@ -1162,12 +1162,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'other_participant'}</t>
+          <t>other_participant</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Other Participant'}</t>
+          <t>Other Participant</t>
         </is>
       </c>
     </row>
@@ -1179,12 +1179,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'primary_school'}</t>
+          <t>primary_school</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Primary School'}</t>
+          <t>Primary School</t>
         </is>
       </c>
     </row>
@@ -1196,12 +1196,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'secondary_school'}</t>
+          <t>secondary_school</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Secondary School'}</t>
+          <t>Secondary School</t>
         </is>
       </c>
     </row>
@@ -1213,12 +1213,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'other_school'}</t>
+          <t>other_school</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'Other School'}</t>
+          <t>Other School</t>
         </is>
       </c>
     </row>
@@ -1230,12 +1230,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'primary_campus'}</t>
+          <t>primary_campus</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'Primary Campus'}</t>
+          <t>Primary Campus</t>
         </is>
       </c>
     </row>
@@ -1247,12 +1247,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'secondary_campus'}</t>
+          <t>secondary_campus</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'Secondary Campus'}</t>
+          <t>Secondary Campus</t>
         </is>
       </c>
     </row>
@@ -1264,12 +1264,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'other_campus'}</t>
+          <t>other_campus</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'Other Campus'}</t>
+          <t>Other Campus</t>
         </is>
       </c>
     </row>
@@ -1281,12 +1281,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'one-time'}</t>
+          <t>one-time</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'One-time'}</t>
+          <t>One-time</t>
         </is>
       </c>
     </row>
@@ -1298,12 +1298,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'repeatedly'}</t>
+          <t>repeatedly</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 'Repeatedly'}</t>
+          <t>Repeatedly</t>
         </is>
       </c>
     </row>
@@ -1315,12 +1315,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_'multiple_times'}</t>
+          <t>multiple_times</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 'Multiple times'}</t>
+          <t>Multiple times</t>
         </is>
       </c>
     </row>
@@ -1332,12 +1332,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_'group_a'}</t>
+          <t>group_a</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 'Group A'}</t>
+          <t>Group A</t>
         </is>
       </c>
     </row>
@@ -1349,12 +1349,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_'group_b'}</t>
+          <t>group_b</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': 'Group B'}</t>
+          <t>Group B</t>
         </is>
       </c>
     </row>
@@ -1366,12 +1366,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'value':_'other_group'}</t>
+          <t>other_group</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'value': 'Other Group'}</t>
+          <t>Other Group</t>
         </is>
       </c>
     </row>
